--- a/filer/41956712_royaluni.xlsx
+++ b/filer/41956712_royaluni.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,9 +193,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4305,6 +4306,148 @@
       </c>
       <c r="F89" s="13">
         <f>IFERROR($F$29/($F$51+$F$58)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B92" s="17">
+        <f>'pengestrom_raw'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C92" s="17">
+        <f>'pengestrom_raw'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D92" s="17">
+        <f>'pengestrom_raw'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E92" s="17">
+        <f>'pengestrom_raw'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F92" s="17">
+        <f>'pengestrom_raw'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B93" s="17">
+        <f>'pengestrom_raw'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C93" s="17">
+        <f>'pengestrom_raw'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D93" s="17">
+        <f>'pengestrom_raw'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E93" s="17">
+        <f>'pengestrom_raw'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F93" s="17">
+        <f>'pengestrom_raw'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B94" s="17">
+        <f>'pengestrom_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C94" s="17">
+        <f>'pengestrom_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D94" s="17">
+        <f>'pengestrom_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E94" s="17">
+        <f>'pengestrom_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F94" s="17">
+        <f>'pengestrom_raw'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B96">
+        <f>IF(ABS(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C96">
+        <f>IF(ABS(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D96">
+        <f>IF(ABS(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E96">
+        <f>IF(ABS(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F96">
+        <f>IF(ABS(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4353,340 +4496,340 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>8746000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>11487000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>12927000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>15036000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>15723000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>4490000</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>6618000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>7533000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>8648000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>8957000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>4256000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>4869000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>5394000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>6388000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>6766000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>2189000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>2926000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>3158000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3626000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>3638000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>415000</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>427000</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>628000</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>794000</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>926000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>1652000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>1516000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1638000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>1968000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>2202000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>37000</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>18000</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>-6000</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>7000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>10000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>10000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>229000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>26000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>49000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>103000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>260000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>326000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>280000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>1647000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>1785000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>1406000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1865000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>1966000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>349000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>294000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>311000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>401000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>406000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>1298000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>1491000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>1095000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>1464000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>1560000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>426000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>475000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>602000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>761000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>797000</v>
       </c>
     </row>
@@ -4735,850 +4878,850 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n">
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n">
         <v>5161000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>5861000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>7558000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>9469000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>9513000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>4485000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>2734000</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>3680000</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>4662000</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>4749000</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>5120000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>153000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>99000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>34000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>17000</v>
       </c>
-      <c r="F7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>23000</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>79000</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>89000</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>73000</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>65000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>8771000</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>11416000</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>14254000</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>14352000</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>14831000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>780000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>1213000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>1401000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>1340000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>1286000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>1188000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>1500000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>1901000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>1944000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>1918000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>89000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>131000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>165000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>147000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>152000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>86000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>214000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>57000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>103000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>82000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>2143000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>3058000</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>3524000</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>3534000</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>3438000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>10914000</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>14474000</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>17778000</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>17886000</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>18269000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>98000</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>100000</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>100000</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>100000</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>100000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>719000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>1567000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>1519000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>1407000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>1416000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>1805000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>2763000</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>4129000</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>4148000</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>4394000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>3330000</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>5158000</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>5748000</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>6408000</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>6713000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>747000</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>1011000</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>1281000</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>1271000</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>1277000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>11000</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>11000</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>11000</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>11000</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>1277000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>1003000</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>1009000</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>998000</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>986000</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>1009000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>3771000</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>4706000</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>6786000</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>5968000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>6710000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>14000</v>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>11000</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>19000</v>
       </c>
-      <c r="F40" s="16" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>1721000</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>1934000</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>2425000</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>2532000</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>2482000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>1427000</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>1669000</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>1785000</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>1806000</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>1950000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>3801000</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>4610000</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>5244000</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>5510000</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="17" t="n">
         <v>4846000</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>7572000</v>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>9316000</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>12030000</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>11478000</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="F50" s="17" t="n">
         <v>11556000</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>10914000</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>14474000</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>17778000</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>17886000</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>18269000</v>
       </c>
     </row>
@@ -5588,6 +5731,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>1753000</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>1135000</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1777000</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>2189000</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>2385000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-1604000</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-744000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-2925000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-651000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-954000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-146000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-252000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>998000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-1491000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-1454000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
